--- a/Models/Свиньи/results/Свиньи - Результаты прогнозов ХВ.xlsx
+++ b/Models/Свиньи/results/Свиньи - Результаты прогнозов ХВ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,32 +478,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[446.27, 549.78, 698.87]</t>
+          <t>[452.55, 535.04, 559.53]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[314.19, 565.5, 523.64]</t>
+          <t>[553.23, 566.96, 496.85]</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>127.0158473756768</v>
+        <v>70.9070614751916</v>
       </c>
       <c r="G2" t="n">
-        <v>107.6782263208992</v>
+        <v>65.09179711138121</v>
       </c>
       <c r="H2" t="n">
-        <v>26.09441826890377</v>
+        <v>12.14776950461263</v>
       </c>
     </row>
     <row r="3">
@@ -514,32 +514,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[456.62, 581.37, 475.28]</t>
+          <t>[579.8, 605.93, 796.64]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[565.5, 523.64, 515.15]</t>
+          <t>[566.96, 496.85, 488.59]</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>74.78126972188768</v>
+        <v>188.8220377419472</v>
       </c>
       <c r="G3" t="n">
-        <v>68.82590238883472</v>
+        <v>143.3266438370439</v>
       </c>
       <c r="H3" t="n">
-        <v>12.6725334011363</v>
+        <v>29.08990274919064</v>
       </c>
     </row>
     <row r="4">
@@ -550,32 +550,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[650.31, 531.38, 416.75]</t>
+          <t>[600.71, 789.75, 1297.47]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[523.64, 515.15, 309.94]</t>
+          <t>[496.85, 488.59, 480.05]</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>96.12015717760521</v>
+        <v>506.5106576224891</v>
       </c>
       <c r="G4" t="n">
-        <v>83.23629681018529</v>
+        <v>407.4806725079268</v>
       </c>
       <c r="H4" t="n">
-        <v>20.60082152171674</v>
+        <v>84.27359360972901</v>
       </c>
     </row>
     <row r="5">
@@ -586,32 +586,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[488.99, 383.76, 1161.83]</t>
+          <t>[734.57, 1207.56, 319.13]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[515.15, 309.94, 797.36]</t>
+          <t>[488.59, 480.05, 263.72]</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>215.2310614355703</v>
+        <v>444.5389980785678</v>
       </c>
       <c r="G5" t="n">
-        <v>154.8183612105568</v>
+        <v>342.9662954022021</v>
       </c>
       <c r="H5" t="n">
-        <v>24.86871753723927</v>
+        <v>74.30158906696587</v>
       </c>
     </row>
     <row r="6">
@@ -622,32 +622,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[391.91, 1186.3, 1079.08]</t>
+          <t>[1010.19, 267.49, 343.74]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[309.94, 797.36, 945.29]</t>
+          <t>[480.05, 263.72, 340.79]</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>242.1414755040339</v>
+        <v>306.0872240836498</v>
       </c>
       <c r="G6" t="n">
-        <v>201.5700212193559</v>
+        <v>178.9530330380528</v>
       </c>
       <c r="H6" t="n">
-        <v>29.79362256385737</v>
+        <v>37.57660440126736</v>
       </c>
     </row>
     <row r="7">
@@ -658,32 +658,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[1083.82, 986.66, 497.18]</t>
+          <t>[148.57, 191.95, 238.59]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[797.36, 945.29, 553.23]</t>
+          <t>[263.72, 340.79, 447.27]</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>170.2055681956732</v>
+        <v>162.2335282649895</v>
       </c>
       <c r="G7" t="n">
-        <v>127.9589712999842</v>
+        <v>157.5561780785108</v>
       </c>
       <c r="H7" t="n">
-        <v>16.81108223871184</v>
+        <v>44.66502783155224</v>
       </c>
     </row>
     <row r="8">
@@ -694,32 +694,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[853.53, 430.63, 509.34]</t>
+          <t>[284.11, 351.88, 294.24]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[945.29, 553.23, 566.96]</t>
+          <t>[340.79, 447.27, 467.44]</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>94.46366415155964</v>
+        <v>118.7595033334575</v>
       </c>
       <c r="G8" t="n">
-        <v>90.65998344342363</v>
+        <v>108.4246090368647</v>
       </c>
       <c r="H8" t="n">
-        <v>14.01024831283627</v>
+        <v>25.00427012471638</v>
       </c>
     </row>
     <row r="9">
@@ -730,32 +730,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[452.55, 535.04, 559.53]</t>
+          <t>[381.77, 319.04, 244.59]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>[553.23, 566.96, 496.85]</t>
+          <t>[447.27, 467.44, 306.14]</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>70.9070614751916</v>
+        <v>100.1717206466531</v>
       </c>
       <c r="G9" t="n">
-        <v>65.09179711138121</v>
+        <v>91.81974434844763</v>
       </c>
       <c r="H9" t="n">
-        <v>12.14776950461263</v>
+        <v>22.16649373764553</v>
       </c>
     </row>
     <row r="10">
@@ -766,32 +766,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[579.8, 605.93, 796.64]</t>
+          <t>[342.05, 262.11, 783.62]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>[566.96, 496.85, 488.59]</t>
+          <t>[467.44, 306.14, 694.22]</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>188.8220377419472</v>
+        <v>92.47179704147067</v>
       </c>
       <c r="G10" t="n">
-        <v>143.3266438370439</v>
+        <v>86.27303921049014</v>
       </c>
       <c r="H10" t="n">
-        <v>29.08990274919064</v>
+        <v>18.02823143455541</v>
       </c>
     </row>
     <row r="11">
@@ -802,32 +802,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[600.71, 789.75, 1297.47]</t>
+          <t>[306.16, 913.66, 855.14]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>[496.85, 488.59, 480.05]</t>
+          <t>[306.14, 694.22, 803.75]</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>506.5106576224891</v>
+        <v>130.1215442453452</v>
       </c>
       <c r="G11" t="n">
-        <v>407.4806725079268</v>
+        <v>90.28249608829812</v>
       </c>
       <c r="H11" t="n">
-        <v>84.27359360972901</v>
+        <v>12.66954844601993</v>
       </c>
     </row>
     <row r="12">
@@ -838,32 +838,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[22.38, 27.78, 50.54]</t>
+          <t>[7.37, 55.58, 71.6]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>[60.6, 63.5, 133.2]</t>
+          <t>[7.6, 56.7, 80.7]</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>56.47757419392777</v>
+        <v>5.294014407828952</v>
       </c>
       <c r="G12" t="n">
-        <v>52.20093549430703</v>
+        <v>3.480847433107085</v>
       </c>
       <c r="H12" t="n">
-        <v>60.46227456166204</v>
+        <v>5.41553161512436</v>
       </c>
     </row>
     <row r="13">
@@ -874,32 +874,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[43.25, 78.75, 52.19]</t>
+          <t>[56.21, 72.39, 27.05]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[63.5, 133.2, 97.8]</t>
+          <t>[56.7, 80.7, 25.5]</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>42.64394838172031</v>
+        <v>4.888608023571332</v>
       </c>
       <c r="G13" t="n">
-        <v>40.1047627555752</v>
+        <v>3.449864335582377</v>
       </c>
       <c r="H13" t="n">
-        <v>39.80276769417648</v>
+        <v>5.746223491140274</v>
       </c>
     </row>
     <row r="14">
@@ -910,32 +910,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[92.24, 61.25, 10.12]</t>
+          <t>[72.64, 27.15, 43.3]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>[133.2, 97.8, 11.4]</t>
+          <t>[80.7, 25.5, 20.6]</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>31.70481592708558</v>
+        <v>13.94144499157458</v>
       </c>
       <c r="G14" t="n">
-        <v>26.26489267462523</v>
+        <v>10.80319663236098</v>
       </c>
       <c r="H14" t="n">
-        <v>26.45363249515284</v>
+        <v>42.21922820615433</v>
       </c>
     </row>
     <row r="15">
@@ -946,32 +946,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[71.48, 11.71, 140.21]</t>
+          <t>[28.34, 45.18, 84.09]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>[97.8, 11.4, 126.9]</t>
+          <t>[25.5, 20.6, 60.3]</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>17.03267368797518</v>
+        <v>19.81852750236884</v>
       </c>
       <c r="G15" t="n">
-        <v>13.31460454665283</v>
+        <v>17.07213376482026</v>
       </c>
       <c r="H15" t="n">
-        <v>13.36253509479384</v>
+        <v>56.64499919235503</v>
       </c>
     </row>
     <row r="16">
@@ -982,32 +982,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[13.25, 158.87, 46.15]</t>
+          <t>[43.22, 80.79, 74.25]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>[11.4, 126.9, 41.5]</t>
+          <t>[20.6, 60.3, 59.7]</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>18.68111940346933</v>
+        <v>19.51951847283893</v>
       </c>
       <c r="G16" t="n">
-        <v>12.8236188958352</v>
+        <v>19.21839884827951</v>
       </c>
       <c r="H16" t="n">
-        <v>17.54805680487359</v>
+        <v>56.04656890960741</v>
       </c>
     </row>
     <row r="17">
@@ -1018,32 +1018,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[150.57, 43.83, 7.9]</t>
+          <t>[63.37, 57.92, 106.73]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>[126.9, 41.5, 7.6]</t>
+          <t>[60.3, 59.7, 131.5]</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>13.73483012112442</v>
+        <v>14.44694606335067</v>
       </c>
       <c r="G17" t="n">
-        <v>8.765194742478895</v>
+        <v>9.872590292356017</v>
       </c>
       <c r="H17" t="n">
-        <v>9.387003714393504</v>
+        <v>8.968466329152758</v>
       </c>
     </row>
     <row r="18">
@@ -1054,32 +1054,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[40.8, 7.32, 55.22]</t>
+          <t>[56.72, 104.48, 68.43]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>[41.5, 7.6, 56.7]</t>
+          <t>[59.7, 131.5, 97.9]</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.9605590704386662</v>
+        <v>23.14861859004786</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8222658760201629</v>
+        <v>19.82386582784939</v>
       </c>
       <c r="H18" t="n">
-        <v>2.67528801085784</v>
+        <v>18.54731622874883</v>
       </c>
     </row>
     <row r="19">
@@ -1090,32 +1090,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[7.37, 55.58, 71.6]</t>
+          <t>[106.71, 69.93, 8.21]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[7.6, 56.7, 80.7]</t>
+          <t>[131.5, 97.9, 9.2]</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5.294014407828952</v>
+        <v>21.58913340402309</v>
       </c>
       <c r="G19" t="n">
-        <v>3.480847433107085</v>
+        <v>17.92049549979866</v>
       </c>
       <c r="H19" t="n">
-        <v>5.41553161512436</v>
+        <v>19.40976893039531</v>
       </c>
     </row>
     <row r="20">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[56.21, 72.39, 27.05]</t>
+          <t>[76.23, 8.99, 109.29]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[56.7, 80.7, 25.5]</t>
+          <t>[97.9, 9.2, 127.5]</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4.888608023571332</v>
+        <v>16.33892904367855</v>
       </c>
       <c r="G20" t="n">
-        <v>3.449864335582377</v>
+        <v>13.35964332863475</v>
       </c>
       <c r="H20" t="n">
-        <v>5.746223491140274</v>
+        <v>12.88913815552727</v>
       </c>
     </row>
     <row r="21">
@@ -1162,32 +1162,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[72.64, 27.15, 43.3]</t>
+          <t>[9.99, 120.14, 39.32]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>[80.7, 25.5, 20.6]</t>
+          <t>[9.2, 127.5, 41.1]</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>13.94144499157458</v>
+        <v>4.393290815113039</v>
       </c>
       <c r="G21" t="n">
-        <v>10.80319663236098</v>
+        <v>3.308418782462921</v>
       </c>
       <c r="H21" t="n">
-        <v>42.21922820615433</v>
+        <v>6.215667383636887</v>
       </c>
     </row>
     <row r="22">
@@ -1198,32 +1198,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>[154.92, 195.61, 269.08]</t>
+          <t>[143.97, 244.48, 158.78]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>[68.43, 172.15, 73.6]</t>
+          <t>[236.84, 466.77, 290.34]</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>124.1517705494895</v>
+        <v>158.4762098399157</v>
       </c>
       <c r="G22" t="n">
-        <v>101.8081821857217</v>
+        <v>148.9053178879025</v>
       </c>
       <c r="H22" t="n">
-        <v>135.2022932477063</v>
+        <v>44.04883993699259</v>
       </c>
     </row>
     <row r="23">
@@ -1234,32 +1234,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>[158.3, 203.22, 171.38]</t>
+          <t>[275.36, 179.08, 50.09]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>[172.15, 73.6, 115.3]</t>
+          <t>[466.77, 290.34, 9.0]</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>81.9318859410713</v>
+        <v>130.0072784137801</v>
       </c>
       <c r="G23" t="n">
-        <v>66.51870242970533</v>
+        <v>114.5864535247569</v>
       </c>
       <c r="H23" t="n">
-        <v>77.60066503845037</v>
+        <v>178.6116817736975</v>
       </c>
     </row>
     <row r="24">
@@ -1270,32 +1270,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>[206.48, 174.8, 240.09]</t>
+          <t>[202.45, 55.72, 148.42]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>[73.6, 115.3, 105.35]</t>
+          <t>[290.34, 9.0, 156.2]</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>114.5327379968711</v>
+        <v>57.64000970991805</v>
       </c>
       <c r="G24" t="n">
-        <v>109.0418692437179</v>
+        <v>47.46158897192628</v>
       </c>
       <c r="H24" t="n">
-        <v>120.0175178323413</v>
+        <v>184.7705470886928</v>
       </c>
     </row>
     <row r="25">
@@ -1306,32 +1306,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[146.32, 198.16, 181.83]</t>
+          <t>[60.0, 160.7, 66.56]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[115.3, 105.35, 101.19]</t>
+          <t>[9.0, 156.2, 52.7]</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>73.20926104392744</v>
+        <v>30.62244961562334</v>
       </c>
       <c r="G25" t="n">
-        <v>68.15622614952382</v>
+        <v>23.11726772441534</v>
       </c>
       <c r="H25" t="n">
-        <v>64.89701888248491</v>
+        <v>198.6126197022898</v>
       </c>
     </row>
     <row r="26">
@@ -1342,32 +1342,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[184.77, 173.37, 135.52]</t>
+          <t>[106.95, 42.47, 100.82]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>[105.35, 101.19, 101.72]</t>
+          <t>[156.2, 52.7, 102.7]</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>64.96245066115117</v>
+        <v>29.05931247154059</v>
       </c>
       <c r="G26" t="n">
-        <v>61.80149779163414</v>
+        <v>20.45233238405796</v>
       </c>
       <c r="H26" t="n">
-        <v>59.98356376013525</v>
+        <v>17.59121371908623</v>
       </c>
     </row>
     <row r="27">
@@ -1378,32 +1378,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[151.6, 117.82, 162.13]</t>
+          <t>[46.04, 108.46, 60.56]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>[101.19, 101.72, 236.84]</t>
+          <t>[52.7, 102.7, 170.6]</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>52.8575926689647</v>
+        <v>63.73691974568025</v>
       </c>
       <c r="G27" t="n">
-        <v>47.07402333799677</v>
+        <v>40.82111592601817</v>
       </c>
       <c r="H27" t="n">
-        <v>32.39804427626787</v>
+        <v>27.58255491842792</v>
       </c>
     </row>
     <row r="28">
@@ -1414,32 +1414,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[105.83, 145.45, 246.98]</t>
+          <t>[111.13, 62.37, 98.01]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>[101.72, 236.84, 466.77]</t>
+          <t>[102.7, 170.6, 35.4]</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>137.4504717475027</v>
+        <v>72.35546784074988</v>
       </c>
       <c r="G28" t="n">
-        <v>105.096679474921</v>
+        <v>59.75963741588514</v>
       </c>
       <c r="H28" t="n">
-        <v>29.90424233878499</v>
+        <v>82.84213026977879</v>
       </c>
     </row>
     <row r="29">
@@ -1450,32 +1450,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[143.97, 244.48, 158.78]</t>
+          <t>[61.51, 96.52, 102.31]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>[236.84, 466.77, 290.34]</t>
+          <t>[170.6, 35.4, 11.8]</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>158.4762098399157</v>
+        <v>89.12105271521766</v>
       </c>
       <c r="G29" t="n">
-        <v>148.9053178879025</v>
+        <v>86.90581173800467</v>
       </c>
       <c r="H29" t="n">
-        <v>44.04883993699259</v>
+        <v>334.5354940284839</v>
       </c>
     </row>
     <row r="30">
@@ -1486,32 +1486,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[275.36, 179.08, 50.09]</t>
+          <t>[116.67, 125.82, 126.56]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>[466.77, 290.34, 9.0]</t>
+          <t>[35.4, 11.8, 38.0]</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>130.0072784137801</v>
+        <v>95.6524107309384</v>
       </c>
       <c r="G30" t="n">
-        <v>114.5864535247569</v>
+        <v>94.61681014265019</v>
       </c>
       <c r="H30" t="n">
-        <v>178.6116817736975</v>
+        <v>476.2952080063875</v>
       </c>
     </row>
     <row r="31">
@@ -1522,32 +1522,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[202.45, 55.72, 148.42]</t>
+          <t>[100.23, 100.66, 98.23]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[290.34, 9.0, 156.2]</t>
+          <t>[11.8, 38.0, 26.9]</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>57.64000970991805</v>
+        <v>74.90730232304284</v>
       </c>
       <c r="G31" t="n">
-        <v>47.46158897192628</v>
+        <v>74.13809520908701</v>
       </c>
       <c r="H31" t="n">
-        <v>184.7705470886928</v>
+        <v>393.1484557502254</v>
       </c>
     </row>
     <row r="32">
@@ -1558,29 +1558,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[0.52, 0.37, 0.25]</t>
+          <t>[1.86, 0.35, 0.32]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>[0.71, 6.43, 0.0]</t>
+          <t>[3.8, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3.502753505292116</v>
+        <v>1.152472185556551</v>
       </c>
       <c r="G32" t="n">
-        <v>2.166500467353628</v>
+        <v>0.8685626162461834</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1596,29 +1596,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>[0.41, 0.29, 0.24]</t>
+          <t>[0.48, 0.45, 0.16]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>[6.43, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.483625252370848</v>
+        <v>0.3937264620648432</v>
       </c>
       <c r="G33" t="n">
-        <v>2.182626715232326</v>
+        <v>0.3663053078041547</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1634,17 +1634,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>[0.89, 0.82, 0.74]</t>
+          <t>[0.34, 0.07, 0.15]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0.8222900678554953</v>
+        <v>0.2195712811774711</v>
       </c>
       <c r="G34" t="n">
-        <v>0.8200042523229589</v>
+        <v>0.188636260788199</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1672,17 +1672,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>[0.54, 0.47, 0.43]</t>
+          <t>[0.01, 0.08, 0.57]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0.4795911500515582</v>
+        <v>0.3307384871068974</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4775135587596464</v>
+        <v>0.2190842508140692</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1710,17 +1710,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>[0.34, 0.3, 0.29]</t>
+          <t>[0.08, 0.56, 1.73]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0.3139899624973689</v>
+        <v>1.053237124206366</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3133365545593623</v>
+        <v>0.7930765164135577</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1748,29 +1748,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[0.23, 0.22, 2.08]</t>
+          <t>[0.54, 1.7, -0.06]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 3.8]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.009268222047053</v>
+        <v>1.029346930317874</v>
       </c>
       <c r="G37" t="n">
-        <v>0.7237546087827775</v>
+        <v>0.7674981603826856</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1786,29 +1786,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>[0.17, 1.95, 0.39]</t>
+          <t>[1.46, -0.14, -0.11]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>[0.0, 3.8, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.094935238065506</v>
+        <v>0.8505434832606318</v>
       </c>
       <c r="G38" t="n">
-        <v>0.8049713792168484</v>
+        <v>0.5727039636119441</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1824,29 +1824,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>[1.86, 0.35, 0.32]</t>
+          <t>[-0.27, -0.25, -0.25]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>[3.8, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.152472185556551</v>
+        <v>0.2570486472547105</v>
       </c>
       <c r="G39" t="n">
-        <v>0.8685626162461834</v>
+        <v>0.256834864107654</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1862,17 +1862,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>[0.48, 0.45, 0.16]</t>
+          <t>[-0.19, -0.19, -0.18]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0.3937264620648432</v>
+        <v>0.1867272401088904</v>
       </c>
       <c r="G40" t="n">
-        <v>0.3663053078041547</v>
+        <v>0.1867080576461151</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1900,17 +1900,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>[0.34, 0.07, 0.15]</t>
+          <t>[-0.15, -0.15, -0.14]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0.2195712811774711</v>
+        <v>0.1451343393909121</v>
       </c>
       <c r="G41" t="n">
-        <v>0.188636260788199</v>
+        <v>0.1449960986155655</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1938,32 +1938,32 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>[300.46, 279.39, 371.46]</t>
+          <t>[325.09, 312.08, 332.03]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>[325.4, 324.95, 426.38]</t>
+          <t>[463.17, 399.19, 304.73]</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>43.64189504450034</v>
+        <v>95.56430377861</v>
       </c>
       <c r="G42" t="n">
-        <v>41.80692646426934</v>
+        <v>84.16076584284839</v>
       </c>
       <c r="H42" t="n">
-        <v>11.52198648468463</v>
+        <v>20.1968956783355</v>
       </c>
     </row>
     <row r="43">
@@ -1974,32 +1974,32 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>[285.68, 379.86, 355.67]</t>
+          <t>[348.11, 371.42, 394.05]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>[324.95, 426.38, 407.34]</t>
+          <t>[399.19, 304.73, 310.4]</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>46.10022173639022</v>
+        <v>68.44241579574523</v>
       </c>
       <c r="G43" t="n">
-        <v>45.81906109445896</v>
+        <v>67.13786087394202</v>
       </c>
       <c r="H43" t="n">
-        <v>11.89324738691107</v>
+        <v>20.5426694938188</v>
       </c>
     </row>
     <row r="44">
@@ -2010,32 +2010,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>[393.67, 368.6, 352.93]</t>
+          <t>[389.63, 414.37, 700.52]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>[426.38, 407.34, 371.6]</t>
+          <t>[304.73, 310.4, 513.21]</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>31.19322526932262</v>
+        <v>133.0455549951038</v>
       </c>
       <c r="G44" t="n">
-        <v>30.03809660733994</v>
+        <v>125.3928616515423</v>
       </c>
       <c r="H44" t="n">
-        <v>7.401599621722649</v>
+        <v>32.61764680858897</v>
       </c>
     </row>
     <row r="45">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>[376.87, 360.85, 503.71]</t>
+          <t>[380.3, 646.62, 415.6]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>[407.34, 371.6, 614.91]</t>
+          <t>[310.4, 513.21, 347.69]</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>66.85480780368182</v>
+        <v>95.38775198647599</v>
       </c>
       <c r="G45" t="n">
-        <v>50.80699450066979</v>
+        <v>90.40753387437651</v>
       </c>
       <c r="H45" t="n">
-        <v>9.485909525532914</v>
+        <v>22.68232405501563</v>
       </c>
     </row>
     <row r="46">
@@ -2082,32 +2082,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>[368.86, 514.77, 310.05]</t>
+          <t>[610.47, 392.87, 378.64]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>[371.6, 614.91, 369.74]</t>
+          <t>[513.21, 347.69, 288.64]</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>67.32478032885702</v>
+        <v>80.83297356013784</v>
       </c>
       <c r="G46" t="n">
-        <v>54.18967504463622</v>
+        <v>77.48225588434411</v>
       </c>
       <c r="H46" t="n">
-        <v>11.0554522024476</v>
+        <v>21.0427781163974</v>
       </c>
     </row>
     <row r="47">
@@ -2118,32 +2118,32 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>[515.84, 310.69, 298.69]</t>
+          <t>[374.44, 360.86, 463.14]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>[614.91, 369.74, 463.17]</t>
+          <t>[347.69, 288.64, 272.95]</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>115.9810783835596</v>
+        <v>118.4680706379357</v>
       </c>
       <c r="G47" t="n">
-        <v>107.5328515938314</v>
+        <v>96.3875665671102</v>
       </c>
       <c r="H47" t="n">
-        <v>22.53115424211111</v>
+        <v>34.13157514588968</v>
       </c>
     </row>
     <row r="48">
@@ -2154,32 +2154,32 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>[326.36, 313.8, 301.24]</t>
+          <t>[353.19, 453.23, 423.74]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>[369.74, 463.17, 399.19]</t>
+          <t>[288.64, 272.95, 274.81]</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>106.1246703523604</v>
+        <v>140.0570406057487</v>
       </c>
       <c r="G48" t="n">
-        <v>96.90071871067209</v>
+        <v>131.2537600228547</v>
       </c>
       <c r="H48" t="n">
-        <v>22.83996318412191</v>
+        <v>47.5354957241077</v>
       </c>
     </row>
     <row r="49">
@@ -2190,32 +2190,32 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>[325.09, 312.08, 332.03]</t>
+          <t>[426.22, 398.43, 362.88]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>[463.17, 399.19, 304.73]</t>
+          <t>[272.95, 274.81, 287.1]</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>95.56430377861</v>
+        <v>121.8156280676577</v>
       </c>
       <c r="G49" t="n">
-        <v>84.16076584284839</v>
+        <v>117.5575499387572</v>
       </c>
       <c r="H49" t="n">
-        <v>20.1968956783355</v>
+        <v>42.51097011737644</v>
       </c>
     </row>
     <row r="50">
@@ -2226,32 +2226,32 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>[348.11, 371.42, 394.05]</t>
+          <t>[342.07, 312.04, 488.63]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>[399.19, 304.73, 310.4]</t>
+          <t>[274.81, 287.1, 368.67]</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>68.44241579574523</v>
+        <v>80.70020832352724</v>
       </c>
       <c r="G50" t="n">
-        <v>67.13786087394202</v>
+        <v>70.72288370090945</v>
       </c>
       <c r="H50" t="n">
-        <v>20.5426694938188</v>
+        <v>21.90110476388232</v>
       </c>
     </row>
     <row r="51">
@@ -2262,32 +2262,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>[389.63, 414.37, 700.52]</t>
+          <t>[287.13, 448.01, 258.48]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>[304.73, 310.4, 513.21]</t>
+          <t>[287.1, 368.67, 268.94]</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>133.0455549951038</v>
+        <v>46.20538472617253</v>
       </c>
       <c r="G51" t="n">
-        <v>125.3928616515423</v>
+        <v>29.94394550873108</v>
       </c>
       <c r="H51" t="n">
-        <v>32.61764680858897</v>
+        <v>8.473584019126356</v>
       </c>
     </row>
     <row r="52">
@@ -2298,17 +2298,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>[0.03, -0.14, -0.08]</t>
+          <t>[-0.02, -0.13, -0.11]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0.09381493947222462</v>
+        <v>0.09907872130120249</v>
       </c>
       <c r="G52" t="n">
-        <v>0.08144323116173831</v>
+        <v>0.08637229297734472</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2336,29 +2336,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>[-0.14, -0.08, 0.75]</t>
+          <t>[-0.13, -0.1, -0.27]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 1.4]</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0.4444375782013355</v>
+        <v>0.9705409475301431</v>
       </c>
       <c r="G53" t="n">
-        <v>0.3264351098153231</v>
+        <v>0.6354242396844861</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2374,29 +2374,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>[-0.06, 0.8, 1.31]</t>
+          <t>[-0.08, -0.25, -0.0]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 1.4, 0.0]</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0.886834471007776</v>
+        <v>0.9558364365396205</v>
       </c>
       <c r="G54" t="n">
-        <v>0.722799359237443</v>
+        <v>0.5791879150706551</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2412,29 +2412,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>[0.82, 1.33, 0.3]</t>
+          <t>[-0.24, 0.01, -0.09]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[1.4, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0.9211553656118263</v>
+        <v>0.9491966124072008</v>
       </c>
       <c r="G55" t="n">
-        <v>0.818799836210378</v>
+        <v>0.5804643102209712</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2450,17 +2450,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>[1.09, 0.16, -0.12]</t>
+          <t>[0.26, 0.13, -0.03]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0.6376200981958383</v>
+        <v>0.170083714851856</v>
       </c>
       <c r="G56" t="n">
-        <v>0.4557691540374983</v>
+        <v>0.142084041567366</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2488,17 +2488,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>[0.01, -0.24, -0.07]</t>
+          <t>[0.08, -0.08, -0.02]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0.142640600475028</v>
+        <v>0.06546279846968346</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1041088480005851</v>
+        <v>0.05913109380341373</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2526,17 +2526,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>[-0.24, -0.07, -0.18]</t>
+          <t>[-0.09, -0.03, 0.73]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0.1762577283763111</v>
+        <v>0.4257970165695147</v>
       </c>
       <c r="G58" t="n">
-        <v>0.1622711489726348</v>
+        <v>0.2849375819396717</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2564,17 +2564,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>[-0.02, -0.13, -0.11]</t>
+          <t>[-0.02, 0.76, 1.2]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0.09907872130120249</v>
+        <v>0.8205973144549147</v>
       </c>
       <c r="G59" t="n">
-        <v>0.08637229297734472</v>
+        <v>0.6594623774074594</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2602,29 +2602,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>[-0.13, -0.1, -0.27]</t>
+          <t>[0.77, 1.21, 0.3]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 1.4]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0.9705409475301431</v>
+        <v>0.8440022606126467</v>
       </c>
       <c r="G60" t="n">
-        <v>0.6354242396844861</v>
+        <v>0.7590530723166703</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2640,29 +2640,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>[-0.08, -0.25, -0.0]</t>
+          <t>[0.99, 0.18, -0.08]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>[0.0, 1.4, 0.0]</t>
+          <t>[0.0, 0.0, 2.2]</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0.9558364365396205</v>
+        <v>1.440763969292307</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5791879150706551</v>
+        <v>1.149437721553397</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2678,29 +2678,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>[0.09, 0.03, -0.05]</t>
+          <t>[0.04, 0.07, 0.1]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.1, 0.0]</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0.06388479555427229</v>
+        <v>0.06222232150233847</v>
       </c>
       <c r="G62" t="n">
-        <v>0.05838361342647742</v>
+        <v>0.05519195195035308</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2716,29 +2716,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>[-0.03, -0.11, -0.15]</t>
+          <t>[0.04, 0.07, 0.1]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.1, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0.1091984185605067</v>
+        <v>0.07907326238159787</v>
       </c>
       <c r="G63" t="n">
-        <v>0.09717017867867052</v>
+        <v>0.07654864499352072</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2754,29 +2754,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>[-0.09, -0.13, -0.15]</t>
+          <t>[0.1, 0.14, 0.24]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.1]</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0.1271671996752239</v>
+        <v>0.1284617715221504</v>
       </c>
       <c r="G64" t="n">
-        <v>0.1245637743289941</v>
+        <v>0.1274107386700473</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -2792,29 +2792,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>[-0.08, -0.11, -0.11]</t>
+          <t>[0.07, 0.17, 0.12]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.1, 0.0]</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0.1021746351166608</v>
+        <v>0.09198081209033102</v>
       </c>
       <c r="G65" t="n">
-        <v>0.1013713335719066</v>
+        <v>0.08873199901268812</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -2830,29 +2830,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>[-0.06, -0.07, -0.05]</t>
+          <t>[0.12, 0.08, 0.06]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.1, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0.05925712746234831</v>
+        <v>0.05700025377654959</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0588938890474032</v>
+        <v>0.05238853713916435</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -2868,17 +2868,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>[-0.03, -0.01, 0.02]</t>
+          <t>[0.06, 0.05, -0.01]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0.02280783172619731</v>
+        <v>0.04565241110285482</v>
       </c>
       <c r="G67" t="n">
-        <v>0.02145355022949802</v>
+        <v>0.04029527837855366</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -2906,29 +2906,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[0.01, 0.04, 0.07]</t>
+          <t>[0.01, -0.05, -0.1]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.1]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0.03001217221314695</v>
+        <v>0.06342088811943432</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02620558248063811</v>
+        <v>0.05110017498978712</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -2944,29 +2944,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>[0.04, 0.07, 0.1]</t>
+          <t>[-0.05, -0.1, -0.13]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>[0.0, 0.1, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0.06222232150233847</v>
+        <v>0.09854413200786573</v>
       </c>
       <c r="G69" t="n">
-        <v>0.05519195195035308</v>
+        <v>0.09387046533524175</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -2982,29 +2982,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>[0.04, 0.07, 0.1]</t>
+          <t>[-0.07, -0.1, -0.11]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>[0.1, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0.07907326238159787</v>
+        <v>0.09460591121781428</v>
       </c>
       <c r="G70" t="n">
-        <v>0.07654864499352072</v>
+        <v>0.09278844551799346</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3020,29 +3020,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[0.1, 0.14, 0.24]</t>
+          <t>[-0.06, -0.08, -0.07]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.1]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0.1284617715221504</v>
+        <v>0.07023265730680141</v>
       </c>
       <c r="G71" t="n">
-        <v>0.1274107386700473</v>
+        <v>0.06985896154621024</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -3058,32 +3058,32 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>[5.97, 5.16, 6.1]</t>
+          <t>[1.57, 3.49, 5.18]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>[3.3, 3.1, 2.0]</t>
+          <t>[0.9, 5.4, 10.8]</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3.06491104198511</v>
+        <v>3.447100058092134</v>
       </c>
       <c r="G72" t="n">
-        <v>2.943296133706804</v>
+        <v>2.733250898568894</v>
       </c>
       <c r="H72" t="n">
-        <v>117.4558756624685</v>
+        <v>54.01268178929413</v>
       </c>
     </row>
     <row r="73">
@@ -3094,32 +3094,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>[3.47, 4.18, 3.56]</t>
+          <t>[2.66, 4.06, 2.59]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>[3.1, 2.0, 2.3]</t>
+          <t>[5.4, 10.8, 6.3]</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1.468656484732574</v>
+        <v>4.71543567799059</v>
       </c>
       <c r="G73" t="n">
-        <v>1.270566514851547</v>
+        <v>4.396691335749743</v>
       </c>
       <c r="H73" t="n">
-        <v>58.58297509559303</v>
+        <v>57.34357202626704</v>
       </c>
     </row>
     <row r="74">
@@ -3130,32 +3130,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>[3.89, 3.32, 2.19]</t>
+          <t>[6.3, 4.15, 9.15]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>[2.0, 2.3, 1.1]</t>
+          <t>[10.8, 6.3, 20.2]</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1.388322252135813</v>
+        <v>7.001077601568882</v>
       </c>
       <c r="G74" t="n">
-        <v>1.330769093139399</v>
+        <v>5.899947659805836</v>
       </c>
       <c r="H74" t="n">
-        <v>79.15063522296984</v>
+        <v>43.48248749478081</v>
       </c>
     </row>
     <row r="75">
@@ -3166,32 +3166,32 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>[2.12, 1.32, 1.58]</t>
+          <t>[6.14, 12.99, 3.84]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>[2.3, 1.1, 1.5]</t>
+          <t>[6.3, 20.2, 3.3]</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0.1690073988271654</v>
+        <v>4.174140984634547</v>
       </c>
       <c r="G75" t="n">
-        <v>0.1586391045953467</v>
+        <v>2.635807586181262</v>
       </c>
       <c r="H75" t="n">
-        <v>10.96255130573066</v>
+        <v>18.17465273979412</v>
       </c>
     </row>
     <row r="76">
@@ -3202,32 +3202,32 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>[1.4, 1.68, 2.02]</t>
+          <t>[13.21, 3.91, 3.42]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>[1.1, 1.5, 1.3]</t>
+          <t>[20.2, 3.3, 3.1]</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>0.4624219820477614</v>
+        <v>4.055364713502333</v>
       </c>
       <c r="G76" t="n">
-        <v>0.3997768950179206</v>
+        <v>2.640164293984301</v>
       </c>
       <c r="H76" t="n">
-        <v>31.57035595952005</v>
+        <v>21.14019399027606</v>
       </c>
     </row>
     <row r="77">
@@ -3238,32 +3238,32 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>[1.45, 1.76, 1.89]</t>
+          <t>[5.45, 4.79, 5.19]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>[1.5, 1.3, 0.9]</t>
+          <t>[3.3, 3.1, 0.7]</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0.633756637717768</v>
+        <v>3.035062941402717</v>
       </c>
       <c r="G77" t="n">
-        <v>0.5036947307730969</v>
+        <v>2.776105649763528</v>
       </c>
       <c r="H77" t="n">
-        <v>49.88072186988308</v>
+        <v>253.6793999737835</v>
       </c>
     </row>
     <row r="78">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>[1.8, 1.93, 4.11]</t>
+          <t>[3.41, 3.73, 3.34]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>[1.3, 0.9, 5.4]</t>
+          <t>[3.1, 0.7, 1.0]</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>0.9972614435533204</v>
+        <v>2.216908280446213</v>
       </c>
       <c r="G78" t="n">
-        <v>0.9423831071663047</v>
+        <v>1.892079613331042</v>
       </c>
       <c r="H78" t="n">
-        <v>59.20769285547495</v>
+        <v>225.5593603614367</v>
       </c>
     </row>
     <row r="79">
@@ -3310,32 +3310,32 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>[1.57, 3.49, 5.18]</t>
+          <t>[3.51, 3.13, 1.98]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>[0.9, 5.4, 10.8]</t>
+          <t>[0.7, 1.0, 1.1]</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>3.447100058092134</v>
+        <v>2.098945762442948</v>
       </c>
       <c r="G79" t="n">
-        <v>2.733250898568894</v>
+        <v>1.940822516749749</v>
       </c>
       <c r="H79" t="n">
-        <v>54.01268178929413</v>
+        <v>231.5447107101039</v>
       </c>
     </row>
     <row r="80">
@@ -3346,32 +3346,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>[2.66, 4.06, 2.59]</t>
+          <t>[1.13, 0.55, 0.75]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>[5.4, 10.8, 6.3]</t>
+          <t>[1.0, 1.1, 0.9]</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>4.71543567799059</v>
+        <v>0.3361119613449483</v>
       </c>
       <c r="G80" t="n">
-        <v>4.396691335749743</v>
+        <v>0.2757354122287227</v>
       </c>
       <c r="H80" t="n">
-        <v>57.34357202626704</v>
+        <v>26.45269184724612</v>
       </c>
     </row>
     <row r="81">
@@ -3382,32 +3382,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>[6.3, 4.15, 9.15]</t>
+          <t>[0.48, 0.68, 0.85]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>[10.8, 6.3, 20.2]</t>
+          <t>[1.1, 0.9, 0.8]</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>7.001077601568882</v>
+        <v>0.3799096775435162</v>
       </c>
       <c r="G81" t="n">
-        <v>5.899947659805836</v>
+        <v>0.2962166116897075</v>
       </c>
       <c r="H81" t="n">
-        <v>43.48248749478081</v>
+        <v>28.98079600957701</v>
       </c>
     </row>
     <row r="82">
@@ -3418,32 +3418,32 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>[37.07, 27.18, 29.89]</t>
+          <t>[24.51, 51.75, 42.64]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>[48.0, 30.2, 24.9]</t>
+          <t>[13.9, 51.0, 27.4]</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>7.151878396688572</v>
+        <v>10.7293713621229</v>
       </c>
       <c r="G82" t="n">
-        <v>6.311659015150849</v>
+        <v>8.86694111440727</v>
       </c>
       <c r="H82" t="n">
-        <v>17.59742933797275</v>
+        <v>44.47491443735084</v>
       </c>
     </row>
     <row r="83">
@@ -3454,32 +3454,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>[31.19, 34.24, 35.85]</t>
+          <t>[31.75, 29.43, 29.06]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>[30.2, 24.9, 29.4]</t>
+          <t>[51.0, 27.4, 52.0]</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>6.575896433546904</v>
+        <v>17.32660225236143</v>
       </c>
       <c r="G83" t="n">
-        <v>5.592482979107751</v>
+        <v>14.73790720250813</v>
       </c>
       <c r="H83" t="n">
-        <v>20.90520703018506</v>
+        <v>29.75283895199908</v>
       </c>
     </row>
     <row r="84">
@@ -3490,32 +3490,32 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>[33.66, 35.25, 27.71]</t>
+          <t>[37.03, 38.64, 19.96]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>[24.9, 29.4, 13.3]</t>
+          <t>[27.4, 52.0, 26.9]</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>10.30459678270016</v>
+        <v>10.31810908952223</v>
       </c>
       <c r="G84" t="n">
-        <v>9.673378298367721</v>
+        <v>9.97625902325821</v>
       </c>
       <c r="H84" t="n">
-        <v>54.47025751470812</v>
+        <v>28.87624060300245</v>
       </c>
     </row>
     <row r="85">
@@ -3526,32 +3526,32 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>[30.16, 23.71, 49.8]</t>
+          <t>[32.85, 16.93, 23.33]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>[29.4, 13.3, 79.9]</t>
+          <t>[52.0, 26.9, 48.1]</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>18.39522544455429</v>
+        <v>18.97089474995356</v>
       </c>
       <c r="G85" t="n">
-        <v>13.75876294764218</v>
+        <v>17.96246027769889</v>
       </c>
       <c r="H85" t="n">
-        <v>39.51357870519296</v>
+        <v>41.79159671188786</v>
       </c>
     </row>
     <row r="86">
@@ -3562,32 +3562,32 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>[23.39, 49.15, 26.88]</t>
+          <t>[21.18, 28.78, 18.11]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>[13.3, 79.9, 19.0]</t>
+          <t>[26.9, 48.1, 30.3]</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>19.22984072889553</v>
+        <v>13.59798914179419</v>
       </c>
       <c r="G86" t="n">
-        <v>16.24102292575818</v>
+        <v>12.41048204608175</v>
       </c>
       <c r="H86" t="n">
-        <v>51.95431117402779</v>
+        <v>33.88683544636056</v>
       </c>
     </row>
     <row r="87">
@@ -3598,32 +3598,32 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>[36.92, 20.13, 18.94]</t>
+          <t>[32.74, 20.77, 22.9]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>[79.9, 19.0, 13.9]</t>
+          <t>[48.1, 30.3, 25.1]</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>24.99302106363392</v>
+        <v>10.51157077530398</v>
       </c>
       <c r="G87" t="n">
-        <v>16.38490270652527</v>
+        <v>9.02965257072252</v>
       </c>
       <c r="H87" t="n">
-        <v>32.00953781872977</v>
+        <v>24.0515410852105</v>
       </c>
     </row>
     <row r="88">
@@ -3634,32 +3634,32 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>[30.02, 28.18, 49.78]</t>
+          <t>[26.02, 28.84, 31.58]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>[19.0, 13.9, 51.0]</t>
+          <t>[30.3, 25.1, 29.7]</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>10.43950637396846</v>
+        <v>3.457309559212002</v>
       </c>
       <c r="G88" t="n">
-        <v>8.842671904346853</v>
+        <v>3.30138733668774</v>
       </c>
       <c r="H88" t="n">
-        <v>54.38513155435675</v>
+        <v>11.78962592451073</v>
       </c>
     </row>
     <row r="89">
@@ -3670,32 +3670,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>[24.51, 51.75, 42.64]</t>
+          <t>[31.52, 34.39, 21.73]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>[13.9, 51.0, 27.4]</t>
+          <t>[25.1, 29.7, 13.3]</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>10.7293713621229</v>
+        <v>6.689724909335276</v>
       </c>
       <c r="G89" t="n">
-        <v>8.86694111440727</v>
+        <v>6.513108562317352</v>
       </c>
       <c r="H89" t="n">
-        <v>44.47491443735084</v>
+        <v>34.91445027344217</v>
       </c>
     </row>
     <row r="90">
@@ -3706,32 +3706,32 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>[31.75, 29.43, 29.06]</t>
+          <t>[30.49, 19.02, 74.21]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>[51.0, 27.4, 52.0]</t>
+          <t>[29.7, 13.3, 83.2]</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>17.32660225236143</v>
+        <v>6.169973505213004</v>
       </c>
       <c r="G90" t="n">
-        <v>14.73790720250813</v>
+        <v>5.166580028562798</v>
       </c>
       <c r="H90" t="n">
-        <v>29.75283895199908</v>
+        <v>18.82723423104347</v>
       </c>
     </row>
     <row r="91">
@@ -3742,32 +3742,32 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>[37.03, 38.64, 19.96]</t>
+          <t>[18.77, 73.18, 24.15]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>[27.4, 52.0, 26.9]</t>
+          <t>[13.3, 83.2, 5.0]</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>10.31810908952223</v>
+        <v>12.86907448843442</v>
       </c>
       <c r="G91" t="n">
-        <v>9.97625902325821</v>
+        <v>11.5441502298482</v>
       </c>
       <c r="H91" t="n">
-        <v>28.87624060300245</v>
+        <v>145.350936659639</v>
       </c>
     </row>
     <row r="92">
@@ -3778,32 +3778,32 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>[100.91, 169.33, 207.44]</t>
+          <t>[148.82, 148.4, 138.58]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>[143.6, 172.9, 233.8]</t>
+          <t>[167.7, 169.6, 174.8]</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>29.04153741244655</v>
+        <v>26.56993498050397</v>
       </c>
       <c r="G92" t="n">
-        <v>24.20553346255098</v>
+        <v>25.43311698609135</v>
       </c>
       <c r="H92" t="n">
-        <v>14.355649472897</v>
+        <v>14.82618608952108</v>
       </c>
     </row>
     <row r="93">
@@ -3814,32 +3814,32 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>[182.5, 223.41, 181.7]</t>
+          <t>[151.89, 141.82, 154.06]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>[172.9, 233.8, 190.8]</t>
+          <t>[169.6, 174.8, 155.9]</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>9.714372860398576</v>
+        <v>21.63829487385031</v>
       </c>
       <c r="G93" t="n">
-        <v>9.699792661885681</v>
+        <v>17.50972719606177</v>
       </c>
       <c r="H93" t="n">
-        <v>4.923485547678567</v>
+        <v>10.1631175559375</v>
       </c>
     </row>
     <row r="94">
@@ -3850,32 +3850,32 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>[221.01, 179.74, 206.61]</t>
+          <t>[144.83, 157.3, 210.57]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>[233.8, 190.8, 231.3]</t>
+          <t>[174.8, 155.9, 168.9]</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>17.27507413009695</v>
+        <v>29.64189532342867</v>
       </c>
       <c r="G94" t="n">
-        <v>16.17786930006325</v>
+        <v>24.34305630985676</v>
       </c>
       <c r="H94" t="n">
-        <v>7.312831672857058</v>
+        <v>14.23610386343512</v>
       </c>
     </row>
     <row r="95">
@@ -3886,32 +3886,32 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>[181.79, 208.92, 211.05]</t>
+          <t>[163.07, 218.2, 115.39]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>[190.8, 231.3, 145.13]</t>
+          <t>[155.9, 168.9, 136.6]</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>40.52992903070273</v>
+        <v>31.259414277493</v>
       </c>
       <c r="G95" t="n">
-        <v>32.43916808540703</v>
+        <v>25.89161619149293</v>
       </c>
       <c r="H95" t="n">
-        <v>19.94123511118463</v>
+        <v>16.43713681547447</v>
       </c>
     </row>
     <row r="96">
@@ -3922,32 +3922,32 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>[210.94, 213.11, 175.66]</t>
+          <t>[216.32, 114.41, 185.5]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>[231.3, 145.13, 165.3]</t>
+          <t>[168.9, 136.6, 168.6]</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>41.40743785984803</v>
+        <v>31.76018514338155</v>
       </c>
       <c r="G96" t="n">
-        <v>32.90148305948679</v>
+        <v>28.83423772839365</v>
       </c>
       <c r="H96" t="n">
-        <v>20.63802460380114</v>
+        <v>18.1132762119054</v>
       </c>
     </row>
     <row r="97">
@@ -3958,32 +3958,32 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>[217.07, 178.92, 160.89]</t>
+          <t>[109.2, 177.12, 219.04]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>[145.13, 165.3, 167.7]</t>
+          <t>[136.6, 168.6, 232.8]</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>42.45684433862259</v>
+        <v>18.37443312922572</v>
       </c>
       <c r="G97" t="n">
-        <v>30.79009417310565</v>
+        <v>16.56057748868091</v>
       </c>
       <c r="H97" t="n">
-        <v>20.62342330937157</v>
+        <v>10.34139076545533</v>
       </c>
     </row>
     <row r="98">
@@ -3994,32 +3994,32 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>[165.38, 148.82, 148.41]</t>
+          <t>[184.71, 228.3, 185.71]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>[165.3, 167.7, 169.6]</t>
+          <t>[168.6, 232.8, 213.8]</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>16.38519173405132</v>
+        <v>18.87294296611627</v>
       </c>
       <c r="G98" t="n">
-        <v>13.38331207133517</v>
+        <v>16.23110647516733</v>
       </c>
       <c r="H98" t="n">
-        <v>7.933565848784184</v>
+        <v>8.207841461775596</v>
       </c>
     </row>
     <row r="99">
@@ -4030,32 +4030,32 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>[148.82, 148.4, 138.58]</t>
+          <t>[224.48, 182.63, 210.98]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>[167.7, 169.6, 174.8]</t>
+          <t>[232.8, 213.8, 223.4]</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>26.56993498050397</v>
+        <v>19.96050464985324</v>
       </c>
       <c r="G99" t="n">
-        <v>25.43311698609135</v>
+        <v>17.30525535879235</v>
       </c>
       <c r="H99" t="n">
-        <v>14.82618608952108</v>
+        <v>7.905015665607857</v>
       </c>
     </row>
     <row r="100">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>[151.89, 141.82, 154.06]</t>
+          <t>[183.85, 212.38, 204.6]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>[169.6, 174.8, 155.9]</t>
+          <t>[213.8, 223.4, 180.1]</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>21.63829487385031</v>
+        <v>23.22965359196754</v>
       </c>
       <c r="G100" t="n">
-        <v>17.50972719606177</v>
+        <v>21.82443455070522</v>
       </c>
       <c r="H100" t="n">
-        <v>10.1631175559375</v>
+        <v>10.84885554574876</v>
       </c>
     </row>
     <row r="101">
@@ -4102,32 +4102,32 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>[144.83, 157.3, 210.57]</t>
+          <t>[218.39, 210.34, 179.05]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>[174.8, 155.9, 168.9]</t>
+          <t>[223.4, 180.1, 166.6]</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>29.64189532342867</v>
+        <v>19.10050400186122</v>
       </c>
       <c r="G101" t="n">
-        <v>24.34305630985676</v>
+        <v>15.89955582853498</v>
       </c>
       <c r="H101" t="n">
-        <v>14.23610386343512</v>
+        <v>8.835042588548919</v>
       </c>
     </row>
     <row r="102">
@@ -4138,32 +4138,32 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>[603.22, 653.84, 744.13]</t>
+          <t>[807.08, 854.96, 907.99]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>[627.0, 771.9, 724.31]</t>
+          <t>[731.19, 799.44, 776.04]</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>70.46650300256883</v>
+        <v>93.54790090693831</v>
       </c>
       <c r="G102" t="n">
-        <v>53.88442236648723</v>
+        <v>87.78777492581123</v>
       </c>
       <c r="H102" t="n">
-        <v>7.274252155414265</v>
+        <v>11.44242833117013</v>
       </c>
     </row>
     <row r="103">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>[660.46, 751.66, 762.15]</t>
+          <t>[834.24, 886.03, 788.69]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>[771.9, 724.31, 791.73]</t>
+          <t>[799.44, 776.04, 871.68]</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>68.41658188725785</v>
+        <v>82.04854869133399</v>
       </c>
       <c r="G103" t="n">
-        <v>56.12210723009779</v>
+        <v>75.92645136453977</v>
       </c>
       <c r="H103" t="n">
-        <v>7.316247014247073</v>
+        <v>9.348979718146939</v>
       </c>
     </row>
     <row r="104">
@@ -4210,32 +4210,32 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>[783.18, 793.95, 876.04]</t>
+          <t>[876.81, 780.59, 1173.89]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>[724.31, 791.73, 799.86]</t>
+          <t>[776.04, 871.68, 934.66]</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>55.60007647295327</v>
+        <v>158.8321320717435</v>
       </c>
       <c r="G104" t="n">
-        <v>45.75814693044273</v>
+        <v>143.6967268557109</v>
       </c>
       <c r="H104" t="n">
-        <v>5.97762882122764</v>
+        <v>16.34350772070502</v>
       </c>
     </row>
     <row r="105">
@@ -4246,32 +4246,32 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>[777.4, 857.86, 825.07]</t>
+          <t>[757.55, 1139.47, 601.22]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>[791.73, 799.86, 804.37]</t>
+          <t>[871.68, 934.66, 614.67]</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>36.50556059289296</v>
+        <v>135.5923075712871</v>
       </c>
       <c r="G105" t="n">
-        <v>31.01064701203878</v>
+        <v>110.7999696251416</v>
       </c>
       <c r="H105" t="n">
-        <v>3.87830686973893</v>
+        <v>12.3984477801814</v>
       </c>
     </row>
     <row r="106">
@@ -4282,32 +4282,32 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>[861.95, 828.86, 631.63]</t>
+          <t>[1179.15, 621.85, 682.56]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>[799.86, 804.37, 745.53]</t>
+          <t>[934.66, 614.67, 650.04]</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>76.21765083861261</v>
+        <v>142.4604562047022</v>
       </c>
       <c r="G106" t="n">
-        <v>66.82587948733654</v>
+        <v>94.72991155632705</v>
       </c>
       <c r="H106" t="n">
-        <v>8.694878716542149</v>
+        <v>10.77631720053149</v>
       </c>
     </row>
     <row r="107">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>[813.37, 619.76, 772.13]</t>
+          <t>[588.68, 646.45, 721.89]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>[804.37, 745.53, 731.19]</t>
+          <t>[614.67, 650.04, 879.3]</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>76.54046486952021</v>
+        <v>92.13486352990452</v>
       </c>
       <c r="G107" t="n">
-        <v>58.57059226659968</v>
+        <v>62.33118664002836</v>
       </c>
       <c r="H107" t="n">
-        <v>7.862687483059043</v>
+        <v>7.560936986145789</v>
       </c>
     </row>
     <row r="108">
@@ -4354,32 +4354,32 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>[618.07, 769.95, 815.96]</t>
+          <t>[653.37, 729.5, 745.4]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>[745.53, 731.19, 799.44]</t>
+          <t>[650.04, 879.3, 1052.23]</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>77.50473804895425</v>
+        <v>197.1403938159775</v>
       </c>
       <c r="G108" t="n">
-        <v>60.91318885088242</v>
+        <v>153.3182040938468</v>
       </c>
       <c r="H108" t="n">
-        <v>8.154623439091194</v>
+        <v>15.56933536852082</v>
       </c>
     </row>
     <row r="109">
@@ -4390,32 +4390,32 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>[807.08, 854.96, 907.99]</t>
+          <t>[728.6, 744.54, 814.78]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>[731.19, 799.44, 776.04]</t>
+          <t>[879.3, 1052.23, 1181.78]</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>93.54790090693831</v>
+        <v>289.8711790625019</v>
       </c>
       <c r="G109" t="n">
-        <v>87.78777492581123</v>
+        <v>275.1322375940453</v>
       </c>
       <c r="H109" t="n">
-        <v>11.44242833117013</v>
+        <v>25.81195381350059</v>
       </c>
     </row>
     <row r="110">
@@ -4426,32 +4426,32 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>[834.24, 886.03, 788.69]</t>
+          <t>[777.53, 850.51, 821.71]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>[799.44, 776.04, 871.68]</t>
+          <t>[1052.23, 1181.78, 1087.37]</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>82.04854869133399</v>
+        <v>291.9870224440421</v>
       </c>
       <c r="G110" t="n">
-        <v>75.92645136453977</v>
+        <v>290.5399203830852</v>
       </c>
       <c r="H110" t="n">
-        <v>9.348979718146939</v>
+        <v>26.1894648960073</v>
       </c>
     </row>
     <row r="111">
@@ -4462,32 +4462,32 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>[876.81, 780.59, 1173.89]</t>
+          <t>[916.08, 884.42, 686.76]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>[776.04, 871.68, 934.66]</t>
+          <t>[1181.78, 1087.37, 842.58]</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>158.8321320717435</v>
+        <v>212.9649398948332</v>
       </c>
       <c r="G111" t="n">
-        <v>143.6967268557109</v>
+        <v>208.1545247623597</v>
       </c>
       <c r="H111" t="n">
-        <v>16.34350772070502</v>
+        <v>19.87996995877626</v>
       </c>
     </row>
     <row r="112">
@@ -4498,32 +4498,32 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>[664.05, 449.2, 101.87]</t>
+          <t>[460.34, 369.06, 611.96]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>[767.11, 529.05, 162.8]</t>
+          <t>[332.33, 272.7, 434.95]</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>83.08974969145547</v>
+        <v>137.84447786103</v>
       </c>
       <c r="G112" t="n">
-        <v>81.28367651531494</v>
+        <v>133.7924061194543</v>
       </c>
       <c r="H112" t="n">
-        <v>21.98576930940825</v>
+        <v>38.18349137514329</v>
       </c>
     </row>
     <row r="113">
@@ -4534,32 +4534,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>[485.88, 110.16, 51.35]</t>
+          <t>[310.71, 516.11, 665.2]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>[529.05, 162.8, 66.3]</t>
+          <t>[272.7, 434.95, 517.61]</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>40.23891484764686</v>
+        <v>99.69140022386182</v>
       </c>
       <c r="G113" t="n">
-        <v>36.91701446604085</v>
+        <v>88.92154366717631</v>
       </c>
       <c r="H113" t="n">
-        <v>21.01144277268391</v>
+        <v>20.37109329807866</v>
       </c>
     </row>
     <row r="114">
@@ -4570,32 +4570,32 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>[115.25, 53.73, 111.96]</t>
+          <t>[480.36, 619.5, 773.45]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>[162.8, 66.3, 133.58]</t>
+          <t>[434.95, 517.61, 528.19]</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>31.01801082045492</v>
+        <v>155.5591968154347</v>
       </c>
       <c r="G114" t="n">
-        <v>27.24695015563335</v>
+        <v>130.8519665853676</v>
       </c>
       <c r="H114" t="n">
-        <v>21.45177512993807</v>
+        <v>25.51939491534808</v>
       </c>
     </row>
     <row r="115">
@@ -4606,32 +4606,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>[64.7, 134.39, 196.52]</t>
+          <t>[586.44, 732.54, 636.73]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>[66.3, 133.58, 166.34]</t>
+          <t>[517.61, 528.19, 829.56]</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>17.45653752420749</v>
+        <v>167.014145810366</v>
       </c>
       <c r="G115" t="n">
-        <v>10.86378507519571</v>
+        <v>155.3381075833109</v>
       </c>
       <c r="H115" t="n">
-        <v>7.054782361192043</v>
+        <v>25.07727718879055</v>
       </c>
     </row>
     <row r="116">
@@ -4642,32 +4642,32 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>[136.2, 199.15, 180.52]</t>
+          <t>[683.35, 594.38, 403.16]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>[133.58, 166.34, 174.56]</t>
+          <t>[528.19, 829.56, 555.74]</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>19.3098653553436</v>
+        <v>184.9904751263002</v>
       </c>
       <c r="G116" t="n">
-        <v>13.79379217423836</v>
+        <v>180.9728529867963</v>
       </c>
       <c r="H116" t="n">
-        <v>8.364936616275065</v>
+        <v>28.39359115626669</v>
       </c>
     </row>
     <row r="117">
@@ -4678,32 +4678,32 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>[197.07, 178.65, 485.7]</t>
+          <t>[513.21, 348.49, 81.48]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>[166.34, 174.56, 332.33]</t>
+          <t>[829.56, 555.74, 195.42]</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>90.33679850981294</v>
+        <v>228.0427303383867</v>
       </c>
       <c r="G117" t="n">
-        <v>62.72776229420182</v>
+        <v>212.5133636544296</v>
       </c>
       <c r="H117" t="n">
-        <v>22.32144626334051</v>
+        <v>44.57808062014352</v>
       </c>
     </row>
     <row r="118">
@@ -4714,32 +4714,32 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>[163.27, 444.33, 356.34]</t>
+          <t>[452.4, 105.75, 48.62]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>[174.56, 332.33, 272.7]</t>
+          <t>[555.74, 195.42, 85.87]</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>80.96682569989726</v>
+        <v>81.86842245307884</v>
       </c>
       <c r="G118" t="n">
-        <v>68.97624796301596</v>
+        <v>76.75252363989524</v>
       </c>
       <c r="H118" t="n">
-        <v>23.61326586460398</v>
+        <v>35.95228442571934</v>
       </c>
     </row>
     <row r="119">
@@ -4750,32 +4750,32 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>[460.34, 369.06, 611.96]</t>
+          <t>[118.55, 54.52, 113.22]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>[332.33, 272.7, 434.95]</t>
+          <t>[195.42, 85.87, 116.23]</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>137.84447786103</v>
+        <v>47.9611368662573</v>
       </c>
       <c r="G119" t="n">
-        <v>133.7924061194543</v>
+        <v>37.07644235856664</v>
       </c>
       <c r="H119" t="n">
-        <v>38.18349137514329</v>
+        <v>26.14512377347105</v>
       </c>
     </row>
     <row r="120">
@@ -4786,32 +4786,32 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>[310.71, 516.11, 665.2]</t>
+          <t>[73.69, 152.32, 218.93]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>[272.7, 434.95, 517.61]</t>
+          <t>[85.87, 116.23, 195.09]</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>99.69140022386182</v>
+        <v>25.94207632134305</v>
       </c>
       <c r="G120" t="n">
-        <v>88.92154366717631</v>
+        <v>24.03586152458973</v>
       </c>
       <c r="H120" t="n">
-        <v>20.37109329807866</v>
+        <v>19.15139771310174</v>
       </c>
     </row>
     <row r="121">
@@ -4822,32 +4822,32 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>[480.36, 619.5, 773.45]</t>
+          <t>[168.02, 241.25, 221.57]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>[434.95, 517.61, 528.19]</t>
+          <t>[116.23, 195.09, 183.42]</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>155.5591968154347</v>
+        <v>45.70835392709674</v>
       </c>
       <c r="G121" t="n">
-        <v>130.8519665853676</v>
+        <v>45.36454185192139</v>
       </c>
       <c r="H121" t="n">
-        <v>25.51939491534808</v>
+        <v>29.67122660456799</v>
       </c>
     </row>
     <row r="122">
@@ -4858,32 +4858,32 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>[7.26, 12.12, 14.77]</t>
+          <t>[3.77, 1.34, 5.56]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>[3.9, 68.6, 3.6]</t>
+          <t>[4.4, 4.6, 13.6]</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>33.29487102151588</v>
+        <v>5.019956649118512</v>
       </c>
       <c r="G122" t="n">
-        <v>23.66993252034714</v>
+        <v>3.974713201569886</v>
       </c>
       <c r="H122" t="n">
-        <v>159.6201111876912</v>
+        <v>48.07259554827241</v>
       </c>
     </row>
     <row r="123">
@@ -4894,32 +4894,32 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>[10.91, 13.44, 6.03]</t>
+          <t>[1.46, 5.88, 2.8]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>[68.6, 3.6, 5.0]</t>
+          <t>[4.6, 13.6, 8.3]</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>33.79388191049136</v>
+        <v>5.76153362386259</v>
       </c>
       <c r="G123" t="n">
-        <v>22.85190322404695</v>
+        <v>5.450406423707601</v>
       </c>
       <c r="H123" t="n">
-        <v>125.9770682134366</v>
+        <v>63.73870513569083</v>
       </c>
     </row>
     <row r="124">
@@ -4930,32 +4930,32 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>[18.26, 8.46, 25.66]</t>
+          <t>[8.01, 3.98, 4.15]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>[3.6, 5.0, 4.4]</t>
+          <t>[13.6, 8.3, 5.2]</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>15.03988068518237</v>
+        <v>4.123088241679366</v>
       </c>
       <c r="G124" t="n">
-        <v>13.124899461527</v>
+        <v>3.653306088549108</v>
       </c>
       <c r="H124" t="n">
-        <v>319.8173530778313</v>
+        <v>37.78648016330015</v>
       </c>
     </row>
     <row r="125">
@@ -4966,32 +4966,32 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>[6.03, 19.49, 11.56]</t>
+          <t>[4.65, 4.88, 2.62]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>[5.0, 4.4, 2.6]</t>
+          <t>[8.3, 5.2, 3.6]</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>10.14825495704605</v>
+        <v>2.190338408462722</v>
       </c>
       <c r="G125" t="n">
-        <v>8.358641823602285</v>
+        <v>1.648255740450416</v>
       </c>
       <c r="H125" t="n">
-        <v>236.0456154090012</v>
+        <v>25.73245422815837</v>
       </c>
     </row>
     <row r="126">
@@ -5002,32 +5002,32 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>[19.16, 11.36, 14.47]</t>
+          <t>[5.53, 2.94, 33.91]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>[4.4, 2.6, 3.1]</t>
+          <t>[5.2, 3.6, 71.1]</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>11.88848245777223</v>
+        <v>21.47392095325679</v>
       </c>
       <c r="G126" t="n">
-        <v>11.63201868506737</v>
+        <v>12.72584331912866</v>
       </c>
       <c r="H126" t="n">
-        <v>346.4495315468479</v>
+        <v>25.6649242554092</v>
       </c>
     </row>
     <row r="127">
@@ -5038,32 +5038,32 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>[10.29, 12.91, 9.57]</t>
+          <t>[2.91, 33.64, 2.77]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>[2.6, 3.1, 4.4]</t>
+          <t>[3.6, 71.1, 3.7]</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>7.790508108789096</v>
+        <v>21.63559981531616</v>
       </c>
       <c r="G127" t="n">
-        <v>7.556345246286348</v>
+        <v>13.02657465987552</v>
       </c>
       <c r="H127" t="n">
-        <v>243.2110645119939</v>
+        <v>32.36225618022696</v>
       </c>
     </row>
     <row r="128">
@@ -5074,32 +5074,32 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>[11.01, 8.06, 3.38]</t>
+          <t>[32.96, 2.99, 3.69]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>[3.1, 4.4, 4.6]</t>
+          <t>[71.1, 3.7, 4.4]</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>5.084650542325564</v>
+        <v>22.02559919808965</v>
       </c>
       <c r="G128" t="n">
-        <v>4.265991954679909</v>
+        <v>13.1830091988188</v>
       </c>
       <c r="H128" t="n">
-        <v>121.6982884027273</v>
+        <v>29.59423816483154</v>
       </c>
     </row>
     <row r="129">
@@ -5110,32 +5110,32 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>[3.77, 1.34, 5.56]</t>
+          <t>[2.62, 3.78, 3.83]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>[4.4, 4.6, 13.6]</t>
+          <t>[3.7, 4.4, 3.2]</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>5.019956649118512</v>
+        <v>0.8055797000190192</v>
       </c>
       <c r="G129" t="n">
-        <v>3.974713201569886</v>
+        <v>0.775868565166975</v>
       </c>
       <c r="H129" t="n">
-        <v>48.07259554827241</v>
+        <v>20.97135013960718</v>
       </c>
     </row>
     <row r="130">
@@ -5146,32 +5146,32 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>[1.46, 5.88, 2.8]</t>
+          <t>[3.94, 4.06, 2.68]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>[4.6, 13.6, 8.3]</t>
+          <t>[4.4, 3.2, 3.0]</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>5.76153362386259</v>
+        <v>0.5945251749668397</v>
       </c>
       <c r="G130" t="n">
-        <v>5.450406423707601</v>
+        <v>0.548443232575055</v>
       </c>
       <c r="H130" t="n">
-        <v>63.73870513569083</v>
+        <v>16.03920011004685</v>
       </c>
     </row>
     <row r="131">
@@ -5182,32 +5182,32 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>[8.01, 3.98, 4.15]</t>
+          <t>[4.11, 2.71, 3.62]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>[13.6, 8.3, 5.2]</t>
+          <t>[3.2, 3.0, 3.2]</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>4.123088241679366</v>
+        <v>0.6026642608681473</v>
       </c>
       <c r="G131" t="n">
-        <v>3.653306088549108</v>
+        <v>0.5404167526314495</v>
       </c>
       <c r="H131" t="n">
-        <v>37.78648016330015</v>
+        <v>17.08883466593666</v>
       </c>
     </row>
     <row r="132">
@@ -5218,17 +5218,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>[-0.32, -0.13, -0.14]</t>
+          <t>[0.38, -0.28, 0.05]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>0.213410780809917</v>
+        <v>0.2746001443711909</v>
       </c>
       <c r="G132" t="n">
-        <v>0.1952873942208909</v>
+        <v>0.2376173468972932</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -5256,17 +5256,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>[-0.02, -0.03, -0.38]</t>
+          <t>[-0.34, -0.04, 0.25]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>0.2223763629539132</v>
+        <v>0.2457109485545734</v>
       </c>
       <c r="G133" t="n">
-        <v>0.14364555071202</v>
+        <v>0.2104410535637267</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -5294,17 +5294,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>[-0.02, -0.38, -0.38]</t>
+          <t>[0.08, 0.41, 0.85]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>0.3123278292784591</v>
+        <v>0.5458979615870297</v>
       </c>
       <c r="G134" t="n">
-        <v>0.2619464942508593</v>
+        <v>0.4451896394708628</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -5332,17 +5332,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>[-0.38, -0.38, 0.17]</t>
+          <t>[0.38, 0.81, -0.09]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5351,10 +5351,10 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>0.3234729166844952</v>
+        <v>0.5189163427556887</v>
       </c>
       <c r="G135" t="n">
-        <v>0.3075571701285196</v>
+        <v>0.4250802680252854</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -5370,17 +5370,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>[-0.29, 0.33, -0.03]</t>
+          <t>[0.66, -0.16, 0.04]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5389,10 +5389,10 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>0.2561690345926708</v>
+        <v>0.3929680034121605</v>
       </c>
       <c r="G136" t="n">
-        <v>0.2183955225121877</v>
+        <v>0.2864509737984284</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -5408,17 +5408,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>[0.48, 0.07, 0.53]</t>
+          <t>[-0.27, -0.1, -0.11]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>0.4167209541082967</v>
+        <v>0.1794239742163288</v>
       </c>
       <c r="G137" t="n">
-        <v>0.3628407508137264</v>
+        <v>0.1601253808029539</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -5446,17 +5446,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>[-0.04, 0.37, -0.29]</t>
+          <t>[-0.01, -0.02, -0.35]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5465,10 +5465,10 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>0.2690797510406394</v>
+        <v>0.2025810430437034</v>
       </c>
       <c r="G138" t="n">
-        <v>0.2318443633442826</v>
+        <v>0.1275974550199678</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -5484,17 +5484,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>[0.38, -0.28, 0.05]</t>
+          <t>[-0.02, -0.35, -0.35]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>0.2746001443711909</v>
+        <v>0.2858417735861615</v>
       </c>
       <c r="G139" t="n">
-        <v>0.2376173468972932</v>
+        <v>0.238571183428111</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -5522,17 +5522,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>[-0.34, -0.04, 0.25]</t>
+          <t>[-0.34, -0.35, 0.15]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5541,10 +5541,10 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>0.2457109485545734</v>
+        <v>0.2962651821095593</v>
       </c>
       <c r="G140" t="n">
-        <v>0.2104410535637267</v>
+        <v>0.2812431607801885</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -5560,17 +5560,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>[0.08, 0.41, 0.85]</t>
+          <t>[-0.27, 0.29, -0.03]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5579,10 +5579,10 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>0.5458979615870297</v>
+        <v>0.2286547006480373</v>
       </c>
       <c r="G141" t="n">
-        <v>0.4451896394708628</v>
+        <v>0.1974869395105627</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -5598,32 +5598,32 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>[40.63, 42.95, 17.82]</t>
+          <t>[17.82, 48.26, 40.21]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>[25.7, 40.9, 23.4]</t>
+          <t>[23.4, 57.0, 51.4]</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>9.276176915813748</v>
+        <v>8.805429365372834</v>
       </c>
       <c r="G142" t="n">
-        <v>7.518765691140017</v>
+        <v>8.50125647599225</v>
       </c>
       <c r="H142" t="n">
-        <v>28.97991037642022</v>
+        <v>20.31337918172557</v>
       </c>
     </row>
     <row r="143">
@@ -5634,32 +5634,32 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>[42.95, 17.82, 48.27]</t>
+          <t>[48.26, 40.21, 163.43]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>[40.9, 23.4, 57.0]</t>
+          <t>[57.0, 51.4, 81.2]</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>6.099848348783673</v>
+        <v>48.17496169053194</v>
       </c>
       <c r="G143" t="n">
-        <v>5.455913702844549</v>
+        <v>34.04952211102412</v>
       </c>
       <c r="H143" t="n">
-        <v>14.72988216690263</v>
+        <v>46.11800783702143</v>
       </c>
     </row>
     <row r="144">
@@ -5670,32 +5670,32 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>[17.82, 48.26, 40.21]</t>
+          <t>[40.21, 163.43, 207.43]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>[23.4, 57.0, 51.4]</t>
+          <t>[51.4, 81.2, 152.1]</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>8.805429365372834</v>
+        <v>57.58731221298729</v>
       </c>
       <c r="G144" t="n">
-        <v>8.50125647599225</v>
+        <v>49.58383928248569</v>
       </c>
       <c r="H144" t="n">
-        <v>20.31337918172557</v>
+        <v>53.1378522394217</v>
       </c>
     </row>
     <row r="145">
@@ -5706,32 +5706,32 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>[48.26, 40.21, 163.43]</t>
+          <t>[163.42, 207.43, 73.4]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>[57.0, 51.4, 81.2]</t>
+          <t>[81.2, 152.1, 76.3]</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>48.17496169053194</v>
+        <v>57.24113373533366</v>
       </c>
       <c r="G145" t="n">
-        <v>34.04952211102412</v>
+        <v>46.81750530600823</v>
       </c>
       <c r="H145" t="n">
-        <v>46.11800783702143</v>
+        <v>47.14584544610022</v>
       </c>
     </row>
     <row r="146">
@@ -5742,1486 +5742,2026 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>[40.21, 163.43, 207.43]</t>
+          <t>[207.41, 73.4, 137.39]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>[51.4, 81.2, 152.1]</t>
+          <t>[152.1, 76.3, 71.3]</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>57.58731221298729</v>
+        <v>49.78213129100876</v>
       </c>
       <c r="G146" t="n">
-        <v>49.58383928248569</v>
+        <v>41.43047317984925</v>
       </c>
       <c r="H146" t="n">
-        <v>53.1378522394217</v>
+        <v>44.28285729223574</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>[966.57, 103.26, 182.8]</t>
+          <t>[73.39, 137.35, 87.89]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>[599.72, 175.68, 189.78]</t>
+          <t>[76.3, 71.3, 94.9]</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>215.9271465595048</v>
+        <v>38.38505742568262</v>
       </c>
       <c r="G147" t="n">
-        <v>148.7495638441234</v>
+        <v>25.32118516588558</v>
       </c>
       <c r="H147" t="n">
-        <v>35.35638660020125</v>
+        <v>34.61008280103785</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>[69.6, 125.74, 126.35]</t>
+          <t>[137.35, 87.89, 125.15]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>[175.68, 189.78, 234.52]</t>
+          <t>[71.3, 94.9, 112.6]</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>94.96369355376964</v>
+        <v>39.02521936242157</v>
       </c>
       <c r="G148" t="n">
-        <v>92.7625610617356</v>
+        <v>28.53540051993674</v>
       </c>
       <c r="H148" t="n">
-        <v>46.74996021620195</v>
+        <v>37.05487626317236</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>[224.51, 220.58, 418.5]</t>
+          <t>[87.9, 125.15, 175.83]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>[189.78, 234.52, 269.1]</t>
+          <t>[94.9, 112.6, 147.4]</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>88.92284051032196</v>
+        <v>18.39084877859083</v>
       </c>
       <c r="G149" t="n">
-        <v>66.02438620286698</v>
+        <v>15.99438945485051</v>
       </c>
       <c r="H149" t="n">
-        <v>26.58777270136102</v>
+        <v>12.60460522976078</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>[199.8, 380.37, 493.89]</t>
+          <t>[125.16, 175.82, 34.9]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>[234.52, 269.1, 222.1]</t>
+          <t>[112.6, 147.4, 30.5]</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>170.743072425341</v>
+        <v>18.11622785308659</v>
       </c>
       <c r="G150" t="n">
-        <v>139.262883711251</v>
+        <v>15.12425344173319</v>
       </c>
       <c r="H150" t="n">
-        <v>59.50998920740037</v>
+        <v>14.94970654109597</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>[415.92, 538.37, 250.98]</t>
+          <t>[175.8, 34.9, 42.25]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>[269.1, 222.1, 175.4]</t>
+          <t>[147.4, 30.5, 23.4]</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>205.9910916444551</v>
+        <v>19.84217587374767</v>
       </c>
       <c r="G151" t="n">
-        <v>179.55664547767</v>
+        <v>17.21531233630747</v>
       </c>
       <c r="H151" t="n">
-        <v>80.01640670643722</v>
+        <v>38.08305664385042</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>[6.02, 1.28, 0.36]</t>
+          <t>[224.51, 220.58, 418.5]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>[0.0, 2.6, 0.4]</t>
+          <t>[189.78, 234.52, 269.1]</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>3.557770635844172</v>
+        <v>88.92284051032196</v>
       </c>
       <c r="G152" t="n">
-        <v>2.459566055528833</v>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>66.02438620286698</v>
+      </c>
+      <c r="H152" t="n">
+        <v>26.58777270136102</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>[0.28, -0.21, 2.92]</t>
+          <t>[199.8, 380.37, 493.89]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>[2.6, 0.4, 1.6]</t>
+          <t>[234.52, 269.1, 222.1]</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1.581085703215849</v>
+        <v>170.743072425341</v>
       </c>
       <c r="G153" t="n">
-        <v>1.417225827929444</v>
+        <v>139.262883711251</v>
       </c>
       <c r="H153" t="n">
-        <v>108.1467934798014</v>
+        <v>59.50998920740037</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>[0.07, 4.25, -0.07]</t>
+          <t>[415.92, 538.37, 250.98]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>[0.4, 1.6, 0.0]</t>
+          <t>[269.1, 222.1, 175.4]</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1.539602508184008</v>
+        <v>205.9910916444551</v>
       </c>
       <c r="G154" t="n">
-        <v>1.015630234199965</v>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>179.55664547767</v>
+      </c>
+      <c r="H154" t="n">
+        <v>80.01640670643722</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>[4.53, -0.03, 1.36]</t>
+          <t>[425.38, 199.67, 61.33]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>[1.6, 0.0, 0.0]</t>
+          <t>[222.1, 175.4, 130.43]</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1.865558781354692</v>
+        <v>124.7498729461801</v>
       </c>
       <c r="G155" t="n">
-        <v>1.439448530188233</v>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>98.88280135147727</v>
+      </c>
+      <c r="H155" t="n">
+        <v>52.78020666711475</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>[-0.16, 1.06, 8.02]</t>
+          <t>[134.17, 41.56, 64.06]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 3.6]</t>
+          <t>[175.4, 130.43, 138.3]</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>2.625757808853967</v>
+        <v>70.96519598205383</v>
       </c>
       <c r="G156" t="n">
-        <v>1.878393714837485</v>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>68.11078809356587</v>
+      </c>
+      <c r="H156" t="n">
+        <v>48.43909694851565</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>[1576.12, 1832.95, 1534.84]</t>
+          <t>[49.01, 74.98, 452.87]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>[1638.33, 1414.67, 1451.52]</t>
+          <t>[130.43, 138.3, 208.34]</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>248.8446545516587</v>
+        <v>153.2275651490563</v>
       </c>
       <c r="G157" t="n">
-        <v>187.9377306189654</v>
+        <v>129.7589997734405</v>
       </c>
       <c r="H157" t="n">
-        <v>13.03496041625582</v>
+        <v>75.19442277842718</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>[1885.91, 1580.68, 1729.66]</t>
+          <t>[123.83, 731.6, 174.41]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>[1414.67, 1451.52, 1837.4]</t>
+          <t>[138.3, 208.34, 165.61]</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>288.8807285520854</v>
+        <v>302.2599529376483</v>
       </c>
       <c r="G158" t="n">
-        <v>236.0462044416316</v>
+        <v>182.1751906818859</v>
       </c>
       <c r="H158" t="n">
-        <v>16.02425944436513</v>
+        <v>88.97687084833507</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>[1274.73, 1386.88, 1296.68]</t>
+          <t>[785.46, 186.89, 251.55]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>[1451.52, 1837.4, 1684.2]</t>
+          <t>[208.34, 165.61, 174.63]</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>357.953434970806</v>
+        <v>336.3733243928497</v>
       </c>
       <c r="G159" t="n">
-        <v>338.2756601786037</v>
+        <v>225.1050011190124</v>
       </c>
       <c r="H159" t="n">
-        <v>19.90268260753284</v>
+        <v>111.3007357561437</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>[1535.19, 1428.29, 1289.57]</t>
+          <t>[111.38, 120.69, 537.27]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>[1837.4, 1684.2, 1563.17]</t>
+          <t>[165.61, 174.63, 590.36]</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>277.8939350947321</v>
+        <v>53.75378509759396</v>
       </c>
       <c r="G160" t="n">
-        <v>277.2385250874397</v>
+        <v>53.75159992675275</v>
       </c>
       <c r="H160" t="n">
-        <v>16.38169126880057</v>
+        <v>24.20818184681066</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>[1613.91, 1449.57, 1764.02]</t>
+          <t>[139.71, 619.13, 154.71]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>[1684.2, 1563.17, 1520.87]</t>
+          <t>[174.63, 590.36, 195.49]</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>160.1723446199514</v>
+        <v>35.16711443143594</v>
       </c>
       <c r="G161" t="n">
-        <v>142.3452306635928</v>
+        <v>34.82338932733984</v>
       </c>
       <c r="H161" t="n">
-        <v>9.142685920047931</v>
+        <v>15.24351440736922</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>[1494.74, 1817.76, 1640.28]</t>
+          <t>[0.07, 4.25, -0.07]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>[1563.17, 1520.87, 1617.42]</t>
+          <t>[0.4, 1.6, 0.0]</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>176.3971851098042</v>
+        <v>1.539602508184008</v>
       </c>
       <c r="G162" t="n">
-        <v>129.3923860917622</v>
-      </c>
-      <c r="H162" t="n">
-        <v>8.437293416512027</v>
+        <v>1.015630234199965</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>[1874.36, 1693.2, 1540.82]</t>
+          <t>[4.53, -0.03, 1.36]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>[1520.87, 1617.42, 1524.98]</t>
+          <t>[1.6, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>208.9237835808844</v>
+        <v>1.865558781354692</v>
       </c>
       <c r="G163" t="n">
-        <v>148.3701220899046</v>
-      </c>
-      <c r="H163" t="n">
-        <v>9.65553112622373</v>
+        <v>1.439448530188233</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>[1463.13, 1330.93, 1457.65]</t>
+          <t>[-0.16, 1.06, 8.02]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>[1617.42, 1524.98, 1793.94]</t>
+          <t>[0.0, 0.0, 3.6]</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>241.214767675691</v>
+        <v>2.625757808853967</v>
       </c>
       <c r="G164" t="n">
-        <v>228.2102634168672</v>
-      </c>
-      <c r="H164" t="n">
-        <v>13.66997581785997</v>
+        <v>1.878393714837485</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>[1427.83, 1563.95, 1742.44]</t>
+          <t>[1.13, 8.32, 0.72]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>[1524.98, 1793.94, 1735.7]</t>
+          <t>[0.0, 3.6, 2.2]</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>144.195676611026</v>
+        <v>2.926078901090278</v>
       </c>
       <c r="G165" t="n">
-        <v>111.2901421872648</v>
-      </c>
-      <c r="H165" t="n">
-        <v>6.526233287203236</v>
+        <v>2.439872341004222</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>[1638.12, 1825.69, 2182.61]</t>
+          <t>[7.04, 0.5, 0.72]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>[1793.94, 1735.7, 1662.16]</t>
+          <t>[3.6, 2.2, 2.1]</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>317.9340879066506</v>
+        <v>2.35727239620054</v>
       </c>
       <c r="G166" t="n">
-        <v>255.4202925179382</v>
+        <v>2.176509483262693</v>
       </c>
       <c r="H166" t="n">
-        <v>15.0607564699943</v>
+        <v>79.64082494858143</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>[1037.68, 945.39, 1098.5]</t>
+          <t>[0.32, 0.53, 0.06]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>[1714.02, 1676.54, 1386.32]</t>
+          <t>[2.2, 2.1, 1.1]</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>598.570174058583</v>
+        <v>1.536222209798646</v>
       </c>
       <c r="G167" t="n">
-        <v>565.1045729794106</v>
+        <v>1.496937908190501</v>
       </c>
       <c r="H167" t="n">
-        <v>34.61054872774248</v>
+        <v>84.95085109154765</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>[1055.61, 1228.39, 1120.09]</t>
+          <t>[0.83, 0.26, -0.25]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>[1676.54, 1386.32, 1497.36]</t>
+          <t>[2.1, 1.1, 0.0]</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>429.2765261093337</v>
+        <v>0.890441905962983</v>
       </c>
       <c r="G168" t="n">
-        <v>385.3800609186545</v>
-      </c>
-      <c r="H168" t="n">
-        <v>24.54159956381252</v>
+        <v>0.7859978445998609</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>[1370.74, 1250.3, 1337.1]</t>
+          <t>[0.38, -0.18, 0.71]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>[1386.32, 1497.36, 1200.8]</t>
+          <t>[1.1, 0.0, 1.3]</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>163.1553904290918</v>
+        <v>0.5434513249293049</v>
       </c>
       <c r="G169" t="n">
-        <v>132.9809931330809</v>
-      </c>
-      <c r="H169" t="n">
-        <v>9.658168534651706</v>
+        <v>0.4927779657596139</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>[1253.76, 1340.79, 1116.54]</t>
+          <t>[-0.11, 0.85, 2.22]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>[1497.36, 1200.8, 1929.55]</t>
+          <t>[0.0, 1.3, 2.2]</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>496.6279964960245</v>
+        <v>0.2687339390357233</v>
       </c>
       <c r="G170" t="n">
-        <v>398.8668450472317</v>
-      </c>
-      <c r="H170" t="n">
-        <v>23.35385249844635</v>
+        <v>0.1936582053904038</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>[1399.96, 1164.03, 2051.25]</t>
+          <t>[0.89, 2.29, 1.39]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>[1200.8, 1929.55, 1807.66]</t>
+          <t>[1.3, 2.2, 2.6]</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>477.8523291411448</v>
+        <v>0.7373599049346915</v>
       </c>
       <c r="G171" t="n">
-        <v>402.7587997351366</v>
+        <v>0.5669895011816829</v>
       </c>
       <c r="H171" t="n">
-        <v>23.2449431938068</v>
+        <v>27.23311243497037</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>[1123.26, 1975.58, 1408.73]</t>
+          <t>[1463.13, 1330.93, 1457.65]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>[1929.55, 1807.66, 1183.77]</t>
+          <t>[1617.42, 1524.98, 1793.94]</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>492.9207251669142</v>
+        <v>241.214767675691</v>
       </c>
       <c r="G172" t="n">
-        <v>399.7254885080574</v>
+        <v>228.2102634168672</v>
       </c>
       <c r="H172" t="n">
-        <v>23.35997320514487</v>
+        <v>13.66997581785997</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>[2233.47, 1592.56, 1471.98]</t>
+          <t>[1427.83, 1563.95, 1742.44]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>[1807.66, 1183.77, 1023.24]</t>
+          <t>[1524.98, 1793.94, 1735.7]</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>428.093199599239</v>
+        <v>144.195676611026</v>
       </c>
       <c r="G173" t="n">
-        <v>427.7802351692961</v>
+        <v>111.2901421872648</v>
       </c>
       <c r="H173" t="n">
-        <v>33.98121134672385</v>
+        <v>6.526233287203236</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>[1510.51, 1397.76, 2501.84]</t>
+          <t>[1638.12, 1825.69, 2182.61]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>[1183.77, 1023.24, 1577.77]</t>
+          <t>[1793.94, 1735.7, 1662.16]</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>605.786285218895</v>
+        <v>317.9340879066506</v>
       </c>
       <c r="G174" t="n">
-        <v>541.7769489268537</v>
+        <v>255.4202925179382</v>
       </c>
       <c r="H174" t="n">
-        <v>40.92375314180889</v>
+        <v>15.0607564699943</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>[1323.06, 2367.0, 1728.91]</t>
+          <t>[1947.82, 2331.34, 1794.46]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>[1023.24, 1577.77, 1243.23]</t>
+          <t>[1735.7, 1662.16, 1227.05]</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>562.3341000576778</v>
+        <v>521.1370233129228</v>
       </c>
       <c r="G175" t="n">
-        <v>524.908582510747</v>
+        <v>482.9039487729519</v>
       </c>
       <c r="H175" t="n">
-        <v>39.46282116753168</v>
+        <v>32.90755230098021</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>[2237.99, 1634.63, 2247.05]</t>
+          <t>[2143.75, 1653.45, 1741.94]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>[1577.77, 1243.23, 2020.1]</t>
+          <t>[1662.16, 1227.05, 1408.94]</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>462.0931675419808</v>
+        <v>418.1825549566708</v>
       </c>
       <c r="G176" t="n">
-        <v>426.1892255928885</v>
+        <v>413.6613338383635</v>
       </c>
       <c r="H176" t="n">
-        <v>28.18739225398333</v>
+        <v>29.1193565908579</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>[0.22, 0.82, 0.98]</t>
+          <t>[1393.95, 1464.08, 1405.68]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>[0.7, 2.3, 2.5]</t>
+          <t>[1227.05, 1408.94, 1867.97]</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1.257201148078322</v>
+        <v>285.5443339220312</v>
       </c>
       <c r="G177" t="n">
-        <v>1.162257033150318</v>
+        <v>228.1106056033893</v>
       </c>
       <c r="H177" t="n">
-        <v>64.83023762869851</v>
+        <v>14.0879129533188</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>[1.19, 1.38, 1.27]</t>
+          <t>[1341.47, 1280.51, 1442.63]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>[2.3, 2.5, 0.7]</t>
+          <t>[1408.94, 1867.97, 1494.22]</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>0.9708361908107473</v>
+        <v>342.6949915271561</v>
       </c>
       <c r="G178" t="n">
-        <v>0.9361844915872085</v>
+        <v>235.5066642824595</v>
       </c>
       <c r="H178" t="n">
-        <v>58.37366662522064</v>
+        <v>13.23017130169253</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>[2.0, 1.85, 1.8]</t>
+          <t>[1325.32, 1493.91, 1332.14]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>[2.5, 0.7, 1.0]</t>
+          <t>[1867.97, 1494.22, 1512.88]</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>0.8620354788844322</v>
+        <v>330.2200317680783</v>
       </c>
       <c r="G179" t="n">
-        <v>0.820405894614443</v>
+        <v>241.234798356459</v>
       </c>
       <c r="H179" t="n">
-        <v>88.41007903305695</v>
+        <v>13.67268810217456</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>[2.12, 2.06, 3.63]</t>
+          <t>[1907.18, 1696.11, 1516.49]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>[0.7, 1.0, 0.0]</t>
+          <t>[1494.22, 1512.88, 1586.88]</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>2.331361160177225</v>
+        <v>263.9861595825595</v>
       </c>
       <c r="G180" t="n">
-        <v>2.035724558857824</v>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>222.1928175052988</v>
+      </c>
+      <c r="H180" t="n">
+        <v>14.72805255977245</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>[1.19, 2.34, 3.3]</t>
+          <t>[1441.08, 1291.08, 1444.37]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>[1.0, 0.0, 5.1]</t>
+          <t>[1512.88, 1586.88, 1529.18]</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1.708612500395522</v>
+        <v>182.4340233663279</v>
       </c>
       <c r="G181" t="n">
-        <v>1.444042355744624</v>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>150.8055762973279</v>
+      </c>
+      <c r="H181" t="n">
+        <v>9.644273004240624</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>[2.17, 3.09, 1.44]</t>
+          <t>[1510.51, 1397.76, 2501.84]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>[0.0, 5.1, 2.2]</t>
+          <t>[1183.77, 1023.24, 1577.77]</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1.765439422571357</v>
+        <v>605.786285218895</v>
       </c>
       <c r="G182" t="n">
-        <v>1.648311094299092</v>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>541.7769489268537</v>
+      </c>
+      <c r="H182" t="n">
+        <v>40.92375314180889</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>[1.06, 0.25, 0.09]</t>
+          <t>[1323.06, 2367.0, 1728.91]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>[5.1, 2.2, 0.5]</t>
+          <t>[1023.24, 1577.77, 1243.23]</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2.599499571038082</v>
+        <v>562.3341000576778</v>
       </c>
       <c r="G183" t="n">
-        <v>2.134235994841672</v>
+        <v>524.908582510747</v>
       </c>
       <c r="H183" t="n">
-        <v>83.53948105452682</v>
+        <v>39.46282116753168</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>[1.26, 0.96, 1.66]</t>
+          <t>[2237.99, 1634.63, 2247.05]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>[2.2, 0.5, 1.6]</t>
+          <t>[1577.77, 1243.23, 2020.1]</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>0.6028987938475108</v>
+        <v>462.0931675419808</v>
       </c>
       <c r="G184" t="n">
-        <v>0.4854729567717966</v>
+        <v>426.1892255928885</v>
       </c>
       <c r="H184" t="n">
-        <v>45.93104180252558</v>
+        <v>28.18739225398333</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>[1.34, 2.18, 4.94]</t>
+          <t>[1514.68, 2082.23, 1722.22]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>[0.5, 1.6, 5.9]</t>
+          <t>[1243.23, 2020.1, 1689.17]</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>0.808696185161479</v>
+        <v>161.9054188338952</v>
       </c>
       <c r="G185" t="n">
-        <v>0.792890662656193</v>
+        <v>122.2119978241548</v>
       </c>
       <c r="H185" t="n">
-        <v>73.43492396839552</v>
+        <v>8.955612887745696</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>[1992.33, 1645.58, 1453.35]</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>[2020.1, 1689.17, 1721.94]</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>157.914951526328</v>
+      </c>
+      <c r="G186" t="n">
+        <v>113.315187502523</v>
+      </c>
+      <c r="H186" t="n">
+        <v>6.51769478168009</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>[1650.92, 1458.16, 1200.59]</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>[1689.17, 1721.94, 1684.0]</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>318.7086519265978</v>
+      </c>
+      <c r="G187" t="n">
+        <v>261.8118133556557</v>
+      </c>
+      <c r="H187" t="n">
+        <v>15.42965964570109</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>[1466.5, 1207.36, 1252.22]</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>[1721.94, 1684.0, 1852.75]</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>466.5728482973312</v>
+      </c>
+      <c r="G188" t="n">
+        <v>444.2031028961835</v>
+      </c>
+      <c r="H188" t="n">
+        <v>25.18377592630166</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>[1253.87, 1300.86, 1075.16]</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>[1684.0, 1852.75, 1591.07]</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>501.9142510687003</v>
+      </c>
+      <c r="G189" t="n">
+        <v>499.3090278932857</v>
+      </c>
+      <c r="H189" t="n">
+        <v>29.25164849252787</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>[1387.16, 1144.97, 1643.83]</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>[1852.75, 1591.07, 1441.53]</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>390.1727281116971</v>
+      </c>
+      <c r="G190" t="n">
+        <v>371.3300802475596</v>
+      </c>
+      <c r="H190" t="n">
+        <v>22.40036646359797</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>[1215.62, 1747.27, 1701.83]</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>[1591.07, 1441.53, 2780.05]</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>682.3992450776717</v>
+      </c>
+      <c r="G191" t="n">
+        <v>586.4716569344549</v>
+      </c>
+      <c r="H191" t="n">
+        <v>27.8637248787967</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
           <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
         <is>
           <t>2024-10</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>[1.26, 0.96, 1.66]</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>[2.2, 0.5, 1.6]</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>0.6028987938475108</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0.4854729567717966</v>
+      </c>
+      <c r="H192" t="n">
+        <v>45.93104180252558</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>[1.34, 2.18, 4.94]</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>[0.5, 1.6, 5.9]</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>0.808696185161479</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0.792890662656193</v>
+      </c>
+      <c r="H193" t="n">
+        <v>73.43492396839552</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
         <is>
           <t>2024-12</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
+      <c r="D194" t="inlineStr">
         <is>
           <t>[1.53, 3.75, 2.85]</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
+      <c r="E194" t="inlineStr">
         <is>
           <t>[1.6, 5.9, 5.7]</t>
         </is>
       </c>
-      <c r="F186" t="n">
+      <c r="F194" t="n">
         <v>2.062277096451476</v>
       </c>
-      <c r="G186" t="n">
+      <c r="G194" t="n">
         <v>1.688984815351388</v>
       </c>
-      <c r="H186" t="n">
+      <c r="H194" t="n">
         <v>30.17922366985815</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>[3.81, 2.9, 0.27]</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>[5.9, 5.7, 0.4]</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>2.019829517310613</v>
+      </c>
+      <c r="G195" t="n">
+        <v>1.674931406719398</v>
+      </c>
+      <c r="H195" t="n">
+        <v>39.22586713493203</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>[3.67, 0.52, 1.36]</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>[5.7, 0.4, 1.1]</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>1.182874588423691</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0.8018981267809254</v>
+      </c>
+      <c r="H196" t="n">
+        <v>29.41927868272564</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>[0.82, 1.83, 2.06]</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>[0.4, 1.1, 1.8]</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>0.5109946674525907</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0.4724125550725592</v>
+      </c>
+      <c r="H197" t="n">
+        <v>62.23370094398435</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>[1.48, 1.68, 1.29]</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>[1.1, 1.8, 0.4]</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>0.5625096233264365</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0.4613241539361563</v>
+      </c>
+      <c r="H198" t="n">
+        <v>87.80856264619146</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>[1.47, 1.11, 1.15]</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>[1.8, 0.4, 0.7]</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>0.5208646331312952</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0.4957475507704206</v>
+      </c>
+      <c r="H199" t="n">
+        <v>86.64835522902234</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>[1.25, 1.28, 1.96]</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>[0.4, 0.7, 0.2]</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>1.175689478343133</v>
+      </c>
+      <c r="G200" t="n">
+        <v>1.062760662263722</v>
+      </c>
+      <c r="H200" t="n">
+        <v>391.2854192352365</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>[0.8, 1.34, 2.78]</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>[0.7, 0.2, 1.4]</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>1.036041616493268</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0.8756538425648603</v>
+      </c>
+      <c r="H201" t="n">
+        <v>228.5172217846581</v>
       </c>
     </row>
   </sheetData>
